--- a/src/main/java/Resources/TD.xlsx
+++ b/src/main/java/Resources/TD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhilash Sharma\IdeaProjects\APIAutomationFramework\src\main\java\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18A88F7-B946-45AD-A035-57C54B577EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE88313D-B212-48D7-8C9B-7CA6DF9D7F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1740" yWindow="1740" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>ID</t>
   </si>
@@ -31,38 +31,14 @@
     <t>BaseUrl</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://restful-booker.herokuapp.com</t>
-    </r>
-  </si>
-  <si>
-    <t>UserName</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Password123</t>
+    <t>https://restful-booker.herokuapp.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -78,14 +54,9 @@
     <font>
       <u/>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <color theme="10"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF1155CC"/>
-      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -105,15 +76,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -331,7 +304,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28" customWidth="1"/>
   </cols>
@@ -353,20 +326,12 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
